--- a/outputs/evaluation/decision/v2/CF_M01/run_3/CF_M01_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M01/run_3/CF_M01_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,101 +471,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AWS is used for infrastructure because it allows the creation of scalable and highly available applications.</t>
+          <t>Amazon Athena is a serverless service that makes it unnecessary to manage infrastructure when there is an increase in the data set and users. In addition, to obtain data quickly, Athena performs queries in parallel.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_02, C_04</t>
+          <t>C_01, Performance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12d. Availability and reliability; 12g. Scalability</t>
+          <t>12a. Speed and latency; Performance</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Amazon Athena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6994</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AD_03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>The objective of these services is to form a data lake where all history is stored to be processed in the analytical module, allowing the system to grow in capacity when data volume increases and scale automatically as data increases.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>R_24, R_25, C_03, C_04</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AU_12, AU_16, AU_18, AU_19</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>44, 45</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>The system must be able to grow in capacity when the data volume increases.; The system scales automatically as data increases.; 12f. Capacity; 12g. Scalability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Cloud Storage Service; Amazon S3; Amazon Athena; AWS Glue</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CF_M01_AD01</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.7308</v>
+        <v>0.6716</v>
       </c>
     </row>
   </sheetData>
